--- a/SANDBOX for pro/Priority.xlsx
+++ b/SANDBOX for pro/Priority.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MSWord\Tojiboyev Xondamir\SANDBOX for pro\Books\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Xondamir\Programming\Git Room\Asosiy\SANDBOX for pro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{863BA7F2-6364-48B1-A1E6-5B30B6CD4684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D096DFE7-2C4D-4F0E-88D9-75020DC26B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-11895" yWindow="9615" windowWidth="21600" windowHeight="11385" xr2:uid="{75563A76-6BA9-4881-9762-06AF46E10425}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{75563A76-6BA9-4881-9762-06AF46E10425}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="36">
   <si>
     <t>Nomi</t>
   </si>
@@ -142,6 +139,9 @@
   </si>
   <si>
     <t>8 ta mavzuga 1 bet konspekt</t>
+  </si>
+  <si>
+    <t>50 ta savol-javob</t>
   </si>
 </sst>
 </file>
@@ -259,7 +259,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -278,9 +278,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -318,7 +318,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -424,7 +424,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -566,7 +566,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -575,15 +575,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC408985-9B7D-4E68-8B6C-CFC6185DE6B1}">
   <dimension ref="B1:G18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.140625" style="2"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="32.7109375" customWidth="1"/>
-    <col min="5" max="5" width="27.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="2"/>
+    <col min="3" max="3" width="17.109375" customWidth="1"/>
+    <col min="4" max="4" width="32.6640625" customWidth="1"/>
+    <col min="5" max="5" width="27.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B1" s="3"/>
       <c r="C1" s="5" t="s">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="4">
         <v>1</v>
       </c>
@@ -621,7 +621,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4">
         <v>2</v>
       </c>
@@ -641,7 +641,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="4">
         <v>3</v>
       </c>
@@ -661,7 +661,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4">
         <v>4</v>
       </c>
@@ -681,7 +681,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4">
         <v>5</v>
       </c>
@@ -701,7 +701,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4">
         <v>6</v>
       </c>
@@ -721,7 +721,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4">
         <v>7</v>
       </c>
@@ -741,7 +741,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4">
         <v>8</v>
       </c>
@@ -761,7 +761,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4">
         <v>9</v>
       </c>
@@ -781,7 +781,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4">
         <v>10</v>
       </c>
@@ -801,7 +801,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4">
         <v>11</v>
       </c>
@@ -821,7 +821,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4">
         <v>12</v>
       </c>
@@ -841,7 +841,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4">
         <v>13</v>
       </c>
@@ -861,7 +861,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4">
         <v>14</v>
       </c>
@@ -881,7 +881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4">
         <v>15</v>
       </c>
@@ -889,7 +889,7 @@
         <v>17</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>24</v>
@@ -901,7 +901,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4">
         <v>16</v>
       </c>
@@ -921,7 +921,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18"/>
     </row>
   </sheetData>
